--- a/fixtures/xlsx/mixed-content/input.xlsx
+++ b/fixtures/xlsx/mixed-content/input.xlsx
@@ -11,7 +11,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>Total</t>
+    <t>Value</t>
   </si>
   <si>
     <t>Rate</t>
@@ -20,7 +20,7 @@
     <t>Metric</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Total</t>
   </si>
   <si>
     <t>Passed</t>
@@ -29,16 +29,16 @@
     <t>Result</t>
   </si>
   <si>
-    <t>Test B</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Test A</t>
   </si>
   <si>
     <t>passed</t>
   </si>
   <si>
-    <t>Test A</t>
-  </si>
-  <si>
-    <t>Name</t>
+    <t>Test B</t>
   </si>
 </sst>
 </file>
@@ -51,12 +51,12 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -87,7 +87,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -95,18 +95,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/mixed-content/input.xlsx
+++ b/fixtures/xlsx/mixed-content/input.xlsx
@@ -11,34 +11,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Rate</t>
+    <t>Total</t>
   </si>
   <si>
     <t>Metric</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Result</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>passed</t>
   </si>
   <si>
     <t>Test A</t>
   </si>
   <si>
-    <t>passed</t>
+    <t>Test B</t>
   </si>
   <si>
-    <t>Test B</t>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -48,10 +48,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -64,7 +64,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -72,7 +72,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <f>B3/B2</f>
@@ -87,7 +87,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -98,15 +98,15 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
